--- a/Vehicle/back_end/app/assets/测试预配置文件.xlsx
+++ b/Vehicle/back_end/app/assets/测试预配置文件.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="61">
   <si>
     <t>核心板卡代号</t>
   </si>
@@ -1240,20 +1240,12 @@
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>3</v>
-      </c>
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>5</v>
-      </c>
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
